--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY231"/>
+  <dimension ref="A1:AZ231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73626347</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165784</t>
         </is>
       </c>
     </row>
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73626350</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628688</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628700</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629227</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629244</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629392</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498667</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165787</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,6 +1857,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628726</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165781</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2034,6 +2099,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165783</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498671</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628685</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2366,6 +2446,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629175</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629390</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2575,6 +2665,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498668</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73625438</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2799,6 +2899,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628708</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2898,6 +3003,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498666</t>
         </is>
       </c>
     </row>
@@ -3012,6 +3122,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73625443</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3124,6 +3239,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73625399</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3236,6 +3356,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73625532</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3343,6 +3468,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629332</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3464,6 +3594,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124695408</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3577,6 +3712,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73624862</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3694,6 +3834,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124705048</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3801,6 +3946,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110107974</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3923,6 +4073,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713462</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4040,6 +4195,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713461</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4147,6 +4307,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333046</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4279,6 +4444,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713459</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4406,6 +4576,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295170</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4519,6 +4694,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629593</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4646,6 +4826,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295236</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4753,6 +4938,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295235</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4860,6 +5050,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333053</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4965,6 +5160,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629632</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5065,6 +5265,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629651</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5196,6 +5401,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295230</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5318,6 +5528,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295231</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5440,6 +5655,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295232</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5562,6 +5782,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295237</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5677,6 +5902,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134942090</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5786,6 +6016,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98638471</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5893,6 +6128,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295241</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6000,6 +6240,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295234</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6107,6 +6352,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295173</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6214,6 +6464,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295228</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6321,6 +6576,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333022</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6428,6 +6688,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333037</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6535,6 +6800,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333023</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6662,6 +6932,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295227</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6769,6 +7044,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333038</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6884,6 +7164,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120247155</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6991,6 +7276,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120247272</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7098,6 +7388,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295174</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7205,6 +7500,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333051</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7312,6 +7612,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295175</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7419,6 +7724,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120247189</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7531,6 +7841,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713502</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7646,6 +7961,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134941821</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7773,6 +8093,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295214</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7880,6 +8205,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295215</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8007,6 +8337,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295213</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8121,6 +8456,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120240303</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8231,6 +8571,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120241378</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8338,6 +8683,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295222</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8445,6 +8795,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295224</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8542,6 +8897,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120240596</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8649,6 +9009,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333043</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8771,6 +9136,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295223</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8878,6 +9248,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333031</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8985,6 +9360,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333025</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9102,6 +9482,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295210</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9234,6 +9619,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295219</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9361,6 +9751,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295226</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9468,6 +9863,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120242128</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9600,6 +10000,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295216</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9727,6 +10132,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295217</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9834,6 +10244,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333040</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9941,6 +10356,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333041</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10048,6 +10468,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333029</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10155,6 +10580,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333030</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10269,6 +10699,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120246947</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10386,6 +10821,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295176</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10493,6 +10933,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333039</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10600,6 +11045,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295177</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10707,6 +11157,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333035</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10814,6 +11269,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295183</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10921,6 +11381,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333042</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11053,6 +11518,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295178</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11180,6 +11650,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295181</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11307,6 +11782,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295180</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11418,6 +11898,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120246835</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11545,6 +12030,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122726917</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11652,6 +12142,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540905</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11759,6 +12254,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540907</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11866,6 +12366,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540909</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11973,6 +12478,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540916</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12087,6 +12597,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318956</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12201,6 +12716,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319853</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12311,6 +12831,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122320519</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12438,6 +12963,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540910</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12565,6 +13095,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540912</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12682,6 +13217,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540903</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12814,6 +13354,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540904</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12946,6 +13491,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540900</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13078,6 +13628,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540902</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13210,6 +13765,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540899</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13326,6 +13886,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319074</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13458,6 +14023,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540913</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13590,6 +14160,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540915</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13722,6 +14297,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540901</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13854,6 +14434,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540908</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13986,6 +14571,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540906</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14097,6 +14687,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319415</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14208,6 +14803,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319322</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14320,6 +14920,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319339</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14431,6 +15036,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319351</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14542,6 +15152,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319380</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14653,6 +15268,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319558</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14764,6 +15384,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319726</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14875,6 +15500,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319795</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14986,6 +15616,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122320250</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15097,6 +15732,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318867</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15209,6 +15849,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318666</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15321,6 +15966,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318675</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15448,6 +16098,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540872</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15584,6 +16239,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540874</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15700,6 +16360,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122325011</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15827,6 +16492,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540873</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15941,6 +16611,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122324295</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16068,6 +16743,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295208</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16179,6 +16859,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122325159</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16286,6 +16971,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333028</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16397,6 +17087,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120242820</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16511,6 +17206,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120242574</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16618,6 +17318,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333049</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16725,6 +17430,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120243000</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16847,6 +17557,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295201</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16961,6 +17676,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120242844</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17075,6 +17795,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120243115</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17182,6 +17907,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295203</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17314,6 +18044,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295207</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17426,6 +18161,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120243180</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17533,6 +18273,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120242814</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17660,6 +18405,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295202</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17767,6 +18517,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333026</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17874,6 +18629,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540885</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17981,6 +18741,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122324459</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18088,6 +18853,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333047</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18202,6 +18972,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122310585</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18309,6 +19084,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333024</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18424,6 +19204,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122310983</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18541,6 +19326,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540895</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18668,6 +19458,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295187</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18795,6 +19590,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295194</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18927,6 +19727,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540883</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -19039,6 +19844,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295184</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19146,6 +19956,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120245354</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19258,6 +20073,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120246044</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19385,6 +20205,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540884</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19504,6 +20329,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122311312</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19611,6 +20441,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295190</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19722,6 +20557,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120245368</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19833,6 +20673,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120245667</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19940,6 +20785,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295189</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20047,6 +20897,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295192</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20154,6 +21009,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295193</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20261,6 +21121,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120333034</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20372,6 +21237,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122311010</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20483,6 +21353,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122311404</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20590,6 +21465,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122323126</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20697,6 +21577,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122323326</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20804,6 +21689,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122323737</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20911,6 +21801,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122323928</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21018,6 +21913,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540887</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21125,6 +22025,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540889</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21232,6 +22137,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540890</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21347,6 +22257,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124203335</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21458,6 +22373,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124203365</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21573,6 +22493,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124203389</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21685,6 +22610,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540886</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21801,6 +22731,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540891</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21913,6 +22848,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295188</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -22020,6 +22960,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295186</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22127,6 +23072,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295195</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22238,6 +23188,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122310912</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22345,6 +23300,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540888</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22452,6 +23412,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540893</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22588,6 +23553,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540897</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22724,6 +23694,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540898</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22838,6 +23813,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945176</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22939,6 +23919,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703499</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -23040,6 +24025,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703561</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -23147,6 +24137,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713478</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23254,6 +24249,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713479</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23364,6 +24364,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944853</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23469,6 +24474,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703528</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23574,6 +24584,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703558</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23679,6 +24694,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703600</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23795,6 +24815,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944776</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23911,6 +24936,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945231</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -24020,6 +25050,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944839</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -24134,6 +25169,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120243641</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -24256,6 +25296,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713483</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -24363,6 +25408,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120243608</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24485,6 +25535,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295199</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24599,6 +25654,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122323827</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24726,6 +25786,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540875</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24853,6 +25918,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540876</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24980,6 +26050,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295200</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -25107,6 +26182,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713482</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -25234,6 +26314,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295197</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -25361,6 +26446,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295198</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -25488,6 +26578,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295196</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25595,6 +26690,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713481</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25732,6 +26832,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713485</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25839,6 +26944,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713484</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25944,6 +27054,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703365</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -26049,6 +27164,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703335</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -26162,6 +27282,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703320</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -26280,6 +27405,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945817</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26380,6 +27510,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703458</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26480,6 +27615,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703463</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26585,6 +27725,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703481</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26695,6 +27840,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124200233</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26797,8 +27947,245 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703543</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -5793,7 +5793,7 @@
         <v>134942090</v>
       </c>
       <c r="B46" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>134941821</v>
       </c>
       <c r="B64" t="n">
-        <v>102496</v>
+        <v>102546</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>134945176</v>
       </c>
       <c r="B196" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>134944853</v>
       </c>
       <c r="B201" t="n">
-        <v>92385</v>
+        <v>92427</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>134944839</v>
       </c>
       <c r="B207" t="n">
-        <v>91993</v>
+        <v>92035</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>134945817</v>
       </c>
       <c r="B226" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99255</v>
+        <v>99272</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99272</v>
+        <v>99273</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99273</v>
+        <v>99274</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99275</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99275</v>
+        <v>99281</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99282</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
